--- a/artfynd/A 28194-2026 artfynd.xlsx
+++ b/artfynd/A 28194-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049051</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -928,6 +938,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049053</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1054,6 +1069,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049054</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1180,6 +1200,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049057</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1304,6 +1329,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034780</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1428,6 +1458,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049052</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1548,6 +1583,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049058</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1664,8 +1704,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034775</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28194-2026 artfynd.xlsx
+++ b/artfynd/A 28194-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135049051</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>135049053</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>135049054</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>135049057</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>135034780</v>
       </c>
       <c r="B6" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>135049052</v>
       </c>
       <c r="B7" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>135049058</v>
       </c>
       <c r="B8" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>135034775</v>
       </c>
       <c r="B9" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28194-2026 artfynd.xlsx
+++ b/artfynd/A 28194-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135049051</v>
       </c>
       <c r="B2" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>135049053</v>
       </c>
       <c r="B3" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>135049054</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>135049057</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>135034780</v>
       </c>
       <c r="B6" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>135049052</v>
       </c>
       <c r="B7" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>135049058</v>
       </c>
       <c r="B8" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>135034775</v>
       </c>
       <c r="B9" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
